--- a/Unity/Assets/Config/Excel/BattleGlobalConfig.xlsx
+++ b/Unity/Assets/Config/Excel/BattleGlobalConfig.xlsx
@@ -27,15 +27,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
   <si>
     <t>Key</t>
   </si>
   <si>
-    <t>章节名称</t>
+    <t>参数类型</t>
   </si>
   <si>
-    <t>地图类型</t>
+    <t>参数值</t>
   </si>
   <si>
     <t>描述</t>
@@ -53,16 +53,13 @@
     <t>string</t>
   </si>
   <si>
-    <t>TestKey1</t>
+    <t>TestMapConfigId</t>
   </si>
   <si>
-    <t>int</t>
+    <t>long</t>
   </si>
   <si>
-    <t>TestKey2</t>
-  </si>
-  <si>
-    <t>Test2Val</t>
+    <t>关联BattleMapConfig表-1</t>
   </si>
 </sst>
 </file>
@@ -999,10 +996,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:F8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="5"/>
+  <dimension ref="A3:F7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="5"/>
   <cols>
-    <col min="3" max="3" width="14.25" customWidth="1"/>
+    <col min="3" max="3" width="17.125" customWidth="1"/>
     <col min="4" max="4" width="23.5" customWidth="1"/>
     <col min="5" max="5" width="19.5" customWidth="1"/>
     <col min="6" max="6" width="19.875" customWidth="1"/>
@@ -1050,7 +1047,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:6">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
@@ -1062,24 +1059,16 @@
       <c r="E6" s="2">
         <v>1</v>
       </c>
+      <c r="F6" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="7" spans="3:5">
-      <c r="C7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
+    <row r="7" spans="1:5">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Unity/Assets/Config/Excel/BattleGlobalConfig.xlsx
+++ b/Unity/Assets/Config/Excel/BattleGlobalConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
   <si>
     <t>Key</t>
   </si>
@@ -60,6 +60,15 @@
   </si>
   <si>
     <t>关联BattleMapConfig表-1</t>
+  </si>
+  <si>
+    <t>TileMapUnitSize</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>Tile的边长</t>
   </si>
 </sst>
 </file>
@@ -1063,12 +1072,21 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:6">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="C7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="2">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>13</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
